--- a/src/zf_NG_brain_annotation_20240922.xlsx
+++ b/src/zf_NG_brain_annotation_20240922.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\其他電腦\My Computer\GlycoMSParser\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A305EC5F-0AA0-4B88-A47A-C37B01ADFCDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0617E8D2-DE93-4B0C-9A9A-81C8A9CB10D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{CFD31651-57D7-40EF-BE95-C7417EC3B9A0}"/>
+    <workbookView xWindow="7500" yWindow="2085" windowWidth="18450" windowHeight="10305" activeTab="1" xr2:uid="{CFD31651-57D7-40EF-BE95-C7417EC3B9A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Glycanlist" sheetId="2" r:id="rId1"/>
@@ -630,10 +630,6 @@
   </si>
   <si>
     <t>MS2scan_no</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">peak </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1003,6 +999,10 @@
   </si>
   <si>
     <t>removed redundant values</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peak</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1552,7 +1552,7 @@
         <v>17</v>
       </c>
       <c r="O2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P2" t="s">
         <v>18</v>
@@ -2175,7 +2175,7 @@
         <v>33</v>
       </c>
       <c r="O15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -2270,12 +2270,12 @@
         <v>30</v>
       </c>
       <c r="O17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
@@ -2317,7 +2317,7 @@
         <v>30</v>
       </c>
       <c r="O18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -2410,7 +2410,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
@@ -2537,7 +2537,7 @@
         <v>30</v>
       </c>
       <c r="O23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -2630,7 +2630,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B26" t="s">
         <v>57</v>
@@ -2716,7 +2716,7 @@
         <v>30</v>
       </c>
       <c r="O27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -2760,7 +2760,7 @@
         <v>30</v>
       </c>
       <c r="O28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -2807,7 +2807,7 @@
         <v>30</v>
       </c>
       <c r="O29" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -2898,7 +2898,7 @@
         <v>30</v>
       </c>
       <c r="O31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -2989,7 +2989,7 @@
         <v>30</v>
       </c>
       <c r="O33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -3080,7 +3080,7 @@
         <v>30</v>
       </c>
       <c r="O35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3168,7 +3168,7 @@
         <v>30</v>
       </c>
       <c r="O37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -3215,7 +3215,7 @@
         <v>30</v>
       </c>
       <c r="O38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -3347,7 +3347,7 @@
         <v>30</v>
       </c>
       <c r="O41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -3479,7 +3479,7 @@
         <v>30</v>
       </c>
       <c r="O44" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -3564,7 +3564,7 @@
         <v>30</v>
       </c>
       <c r="O46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -3613,7 +3613,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D48">
         <f t="shared" ref="D48" si="10">E48+21.9819</f>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="O48" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -3731,7 +3731,7 @@
         <v>30</v>
       </c>
       <c r="O50" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
@@ -3904,7 +3904,7 @@
         <v>30</v>
       </c>
       <c r="O54" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
@@ -3989,7 +3989,7 @@
         <v>30</v>
       </c>
       <c r="O56" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -4080,7 +4080,7 @@
         <v>30</v>
       </c>
       <c r="O58" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
@@ -4127,7 +4127,7 @@
         <v>30</v>
       </c>
       <c r="O59" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
         <v>59</v>
       </c>
       <c r="O60" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -4221,7 +4221,7 @@
         <v>30</v>
       </c>
       <c r="O61" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -4268,7 +4268,7 @@
         <v>30</v>
       </c>
       <c r="O62" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
@@ -4359,7 +4359,7 @@
         <v>30</v>
       </c>
       <c r="O64" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
@@ -4450,7 +4450,7 @@
         <v>30</v>
       </c>
       <c r="O66" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
@@ -4582,7 +4582,7 @@
         <v>30</v>
       </c>
       <c r="O69" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
@@ -4656,25 +4656,25 @@
         <v>146</v>
       </c>
       <c r="C1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1" t="s">
         <v>147</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>148</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>149</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>150</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>151</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>152</v>
-      </c>
-      <c r="I1" t="s">
-        <v>153</v>
       </c>
       <c r="J1" t="s">
         <v>14</v>
@@ -4682,7 +4682,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B2">
         <v>14976</v>
@@ -4697,12 +4697,12 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B3">
         <v>15159</v>
@@ -4717,12 +4717,12 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B4">
         <v>15313</v>
@@ -4737,12 +4737,12 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B5">
         <v>15657</v>
@@ -4757,12 +4757,12 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B6">
         <v>16853</v>
@@ -4777,12 +4777,12 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B7">
         <v>17040</v>
@@ -4797,12 +4797,12 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B8">
         <v>17234</v>
@@ -4817,12 +4817,12 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B9">
         <v>18120</v>
@@ -4837,12 +4837,12 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B10">
         <v>18306</v>
@@ -4857,12 +4857,12 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B11">
         <v>20034</v>
@@ -4877,12 +4877,12 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B12">
         <v>21338</v>
@@ -4897,12 +4897,12 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B13">
         <v>23180</v>
@@ -4917,12 +4917,12 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B14">
         <v>23856</v>
@@ -4937,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -4945,7 +4945,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B15">
         <v>24079</v>
@@ -4960,7 +4960,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -4968,7 +4968,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B16">
         <v>25799</v>
@@ -4983,7 +4983,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -4991,7 +4991,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B17">
         <v>27472</v>
@@ -5006,7 +5006,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G17">
         <v>3</v>
@@ -5029,7 +5029,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5069,7 +5069,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5089,12 +5089,12 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B22">
         <v>16000</v>
@@ -5109,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B23">
         <v>16155</v>
@@ -5132,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B24">
         <v>16654</v>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G24">
         <v>3</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B25">
         <v>16839</v>
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G25">
         <v>3</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B26">
         <v>20272</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G26">
         <v>4</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -5244,7 +5244,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -5264,7 +5264,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -5284,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -5304,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -5324,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -5344,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -5384,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -5404,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -5424,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -5464,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -5484,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -5530,7 +5530,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -5553,7 +5553,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -5573,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -5633,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -5653,7 +5653,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -5673,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -5713,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -5733,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -5753,7 +5753,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -5773,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -5793,7 +5793,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -5813,7 +5813,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -5833,7 +5833,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -5853,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -5873,7 +5873,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -5893,7 +5893,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -5913,7 +5913,7 @@
         <v>0</v>
       </c>
       <c r="F61" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -5933,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -5953,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -5973,7 +5973,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -5993,7 +5993,7 @@
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -6013,7 +6013,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -6033,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -6053,7 +6053,7 @@
         <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -6073,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="F69" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -6093,7 +6093,7 @@
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -6113,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -6133,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="F72" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -6156,7 +6156,7 @@
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -6179,7 +6179,7 @@
         <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G74">
         <v>2</v>
@@ -6202,7 +6202,7 @@
         <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G75">
         <v>2</v>
@@ -6225,7 +6225,7 @@
         <v>1</v>
       </c>
       <c r="F76" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G76">
         <v>2</v>
@@ -6248,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G77">
         <v>2</v>
@@ -6271,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G78">
         <v>2</v>
@@ -6294,7 +6294,7 @@
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G79">
         <v>2</v>
@@ -6317,7 +6317,7 @@
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G80">
         <v>2</v>
@@ -6340,7 +6340,7 @@
         <v>1</v>
       </c>
       <c r="F81" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G81">
         <v>2</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -6386,7 +6386,7 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -6409,7 +6409,7 @@
         <v>0</v>
       </c>
       <c r="F84" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -6432,7 +6432,7 @@
         <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -6455,7 +6455,7 @@
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -6478,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -6501,13 +6501,13 @@
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G88">
         <v>2</v>
       </c>
       <c r="J88" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -6527,13 +6527,13 @@
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G89">
         <v>2</v>
       </c>
       <c r="J89" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -6553,7 +6553,7 @@
         <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -6576,7 +6576,7 @@
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -6599,7 +6599,7 @@
         <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -6622,7 +6622,7 @@
         <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -6642,7 +6642,7 @@
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -6662,7 +6662,7 @@
         <v>1</v>
       </c>
       <c r="F95" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -6682,7 +6682,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -6702,7 +6702,7 @@
         <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -6722,7 +6722,7 @@
         <v>1</v>
       </c>
       <c r="F98" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -6742,7 +6742,7 @@
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -6762,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="F100" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -6782,7 +6782,7 @@
         <v>1</v>
       </c>
       <c r="F101" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -6802,7 +6802,7 @@
         <v>1</v>
       </c>
       <c r="F102" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -6822,7 +6822,7 @@
         <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -6842,7 +6842,7 @@
         <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -6862,7 +6862,7 @@
         <v>1</v>
       </c>
       <c r="F105" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -6882,7 +6882,7 @@
         <v>1</v>
       </c>
       <c r="F106" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -6902,7 +6902,7 @@
         <v>1</v>
       </c>
       <c r="F107" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -6922,7 +6922,7 @@
         <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -6942,7 +6942,7 @@
         <v>1</v>
       </c>
       <c r="F109" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -6962,7 +6962,7 @@
         <v>1</v>
       </c>
       <c r="F110" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -6982,7 +6982,7 @@
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -7002,7 +7002,7 @@
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -7022,7 +7022,7 @@
         <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -7042,7 +7042,7 @@
         <v>1</v>
       </c>
       <c r="F114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -7062,7 +7062,7 @@
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -7082,10 +7082,10 @@
         <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J116" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -7105,7 +7105,7 @@
         <v>1</v>
       </c>
       <c r="F117" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -7125,13 +7125,13 @@
         <v>1</v>
       </c>
       <c r="F118" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G118">
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -7151,13 +7151,13 @@
         <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G119">
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -7177,7 +7177,7 @@
         <v>1</v>
       </c>
       <c r="F120" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G120">
         <v>2</v>
@@ -7200,7 +7200,7 @@
         <v>1</v>
       </c>
       <c r="F121" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G121">
         <v>2</v>
@@ -7223,7 +7223,7 @@
         <v>1</v>
       </c>
       <c r="F122" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G122">
         <v>2</v>
@@ -7246,7 +7246,7 @@
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G123">
         <v>2</v>
@@ -7269,7 +7269,7 @@
         <v>1</v>
       </c>
       <c r="F124" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G124">
         <v>2</v>
@@ -7292,7 +7292,7 @@
         <v>1</v>
       </c>
       <c r="F125" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G125">
         <v>2</v>
@@ -7315,7 +7315,7 @@
         <v>1</v>
       </c>
       <c r="F126" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G126">
         <v>2</v>
@@ -7338,7 +7338,7 @@
         <v>0</v>
       </c>
       <c r="F127" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -7361,7 +7361,7 @@
         <v>1</v>
       </c>
       <c r="F128" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G128">
         <v>2</v>
@@ -7384,7 +7384,7 @@
         <v>1</v>
       </c>
       <c r="F129" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G129">
         <v>2</v>
@@ -7407,7 +7407,7 @@
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G130">
         <v>2</v>
@@ -7430,7 +7430,7 @@
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G131">
         <v>2</v>
@@ -7453,7 +7453,7 @@
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G132">
         <v>2</v>
@@ -7476,7 +7476,7 @@
         <v>1</v>
       </c>
       <c r="F133" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G133">
         <v>2</v>
@@ -7499,10 +7499,10 @@
         <v>1</v>
       </c>
       <c r="F134" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J134" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -7522,7 +7522,7 @@
         <v>1</v>
       </c>
       <c r="F135" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -7542,7 +7542,7 @@
         <v>0</v>
       </c>
       <c r="F136" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -7562,12 +7562,12 @@
         <v>1</v>
       </c>
       <c r="F137" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B138">
         <v>21710</v>
@@ -7582,15 +7582,15 @@
         <v>1</v>
       </c>
       <c r="F138" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J138" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B139">
         <v>21908</v>
@@ -7605,15 +7605,15 @@
         <v>1</v>
       </c>
       <c r="F139" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J139" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B140">
         <v>23329</v>
@@ -7628,15 +7628,15 @@
         <v>1</v>
       </c>
       <c r="F140" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J140" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B141">
         <v>22131</v>
@@ -7651,15 +7651,15 @@
         <v>1</v>
       </c>
       <c r="F141" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J141" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B142">
         <v>22357</v>
@@ -7674,15 +7674,15 @@
         <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J142" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B143">
         <v>21911</v>
@@ -7697,15 +7697,15 @@
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J143" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B144">
         <v>22141</v>
@@ -7720,15 +7720,15 @@
         <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J144" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B145">
         <v>22902</v>
@@ -7743,15 +7743,15 @@
         <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J145" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B146">
         <v>23242</v>
@@ -7766,10 +7766,10 @@
         <v>1</v>
       </c>
       <c r="F146" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J146" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -7789,13 +7789,13 @@
         <v>1</v>
       </c>
       <c r="F147" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G147">
         <v>1</v>
       </c>
       <c r="J147" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -7815,13 +7815,13 @@
         <v>1</v>
       </c>
       <c r="F148" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G148">
         <v>1</v>
       </c>
       <c r="J148" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -7841,13 +7841,13 @@
         <v>1</v>
       </c>
       <c r="F149" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G149">
         <v>2</v>
       </c>
       <c r="J149" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -7867,7 +7867,7 @@
         <v>1</v>
       </c>
       <c r="F150" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G150">
         <v>2</v>
@@ -7890,7 +7890,7 @@
         <v>1</v>
       </c>
       <c r="F151" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G151">
         <v>2</v>
@@ -7913,7 +7913,7 @@
         <v>1</v>
       </c>
       <c r="F152" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G152">
         <v>2</v>
@@ -7936,7 +7936,7 @@
         <v>2</v>
       </c>
       <c r="F153" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G153">
         <v>2</v>
@@ -7959,7 +7959,7 @@
         <v>1</v>
       </c>
       <c r="F154" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G154">
         <v>2</v>
@@ -7982,7 +7982,7 @@
         <v>1</v>
       </c>
       <c r="F155" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G155">
         <v>2</v>
@@ -8005,13 +8005,13 @@
         <v>1</v>
       </c>
       <c r="F156" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G156">
         <v>1</v>
       </c>
       <c r="J156" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -8031,13 +8031,13 @@
         <v>1</v>
       </c>
       <c r="F157" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G157">
         <v>1</v>
       </c>
       <c r="J157" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -8057,7 +8057,7 @@
         <v>1</v>
       </c>
       <c r="F158" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G158">
         <v>2</v>
@@ -8080,7 +8080,7 @@
         <v>1</v>
       </c>
       <c r="F159" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G159">
         <v>2</v>
@@ -8103,7 +8103,7 @@
         <v>1</v>
       </c>
       <c r="F160" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G160">
         <v>2</v>
@@ -8126,7 +8126,7 @@
         <v>1</v>
       </c>
       <c r="F161" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G161">
         <v>2</v>
@@ -8134,7 +8134,7 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B162">
         <v>21595</v>
@@ -8149,15 +8149,15 @@
         <v>1</v>
       </c>
       <c r="F162" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J162" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B163">
         <v>21819</v>
@@ -8172,12 +8172,12 @@
         <v>1</v>
       </c>
       <c r="F163" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B164">
         <v>22086</v>
@@ -8192,12 +8192,12 @@
         <v>1</v>
       </c>
       <c r="F164" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B165">
         <v>22423</v>
@@ -8212,12 +8212,12 @@
         <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B166">
         <v>22735</v>
@@ -8232,12 +8232,12 @@
         <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B167">
         <v>21516</v>
@@ -8252,12 +8252,12 @@
         <v>1</v>
       </c>
       <c r="F167" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B168">
         <v>21729</v>
@@ -8272,12 +8272,12 @@
         <v>1</v>
       </c>
       <c r="F168" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B169">
         <v>22046</v>
@@ -8292,12 +8292,12 @@
         <v>1</v>
       </c>
       <c r="F169" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B170">
         <v>22718</v>
@@ -8312,12 +8312,12 @@
         <v>1</v>
       </c>
       <c r="F170" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B171">
         <v>23046</v>
@@ -8332,12 +8332,12 @@
         <v>1</v>
       </c>
       <c r="F171" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B172">
         <v>23526</v>
@@ -8352,7 +8352,7 @@
         <v>1</v>
       </c>
       <c r="F172" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -8372,7 +8372,7 @@
         <v>0</v>
       </c>
       <c r="F173" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -8392,7 +8392,7 @@
         <v>1</v>
       </c>
       <c r="F174" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -8412,7 +8412,7 @@
         <v>1</v>
       </c>
       <c r="F175" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -8432,7 +8432,7 @@
         <v>1</v>
       </c>
       <c r="F176" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -8452,12 +8452,12 @@
         <v>1</v>
       </c>
       <c r="F177" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B178">
         <v>22715</v>
@@ -8472,12 +8472,12 @@
         <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B179">
         <v>21705</v>
@@ -8492,12 +8492,12 @@
         <v>3</v>
       </c>
       <c r="F179" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B180">
         <v>22600</v>
@@ -8512,12 +8512,12 @@
         <v>2</v>
       </c>
       <c r="F180" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B181">
         <v>22844</v>
@@ -8532,12 +8532,12 @@
         <v>1</v>
       </c>
       <c r="F181" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B182">
         <v>23125</v>
@@ -8552,12 +8552,12 @@
         <v>3</v>
       </c>
       <c r="F182" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B183">
         <v>23936</v>
@@ -8572,7 +8572,7 @@
         <v>2</v>
       </c>
       <c r="F183" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -8592,7 +8592,7 @@
         <v>1</v>
       </c>
       <c r="F184" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -8612,7 +8612,7 @@
         <v>2</v>
       </c>
       <c r="F185" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -8632,7 +8632,7 @@
         <v>1</v>
       </c>
       <c r="F186" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -8652,7 +8652,7 @@
         <v>1</v>
       </c>
       <c r="F187" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -8672,7 +8672,7 @@
         <v>1</v>
       </c>
       <c r="F188" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -8692,7 +8692,7 @@
         <v>1</v>
       </c>
       <c r="F189" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -8712,7 +8712,7 @@
         <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -8732,7 +8732,7 @@
         <v>1</v>
       </c>
       <c r="F191" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -8752,7 +8752,7 @@
         <v>1</v>
       </c>
       <c r="F192" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -8772,7 +8772,7 @@
         <v>1</v>
       </c>
       <c r="F193" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -8792,7 +8792,7 @@
         <v>1</v>
       </c>
       <c r="F194" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -8812,7 +8812,7 @@
         <v>1</v>
       </c>
       <c r="F195" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -8832,7 +8832,7 @@
         <v>1</v>
       </c>
       <c r="F196" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -8852,7 +8852,7 @@
         <v>1</v>
       </c>
       <c r="F197" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -8872,7 +8872,7 @@
         <v>1</v>
       </c>
       <c r="F198" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -8892,7 +8892,7 @@
         <v>1</v>
       </c>
       <c r="F199" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -8912,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="F200" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -8932,7 +8932,7 @@
         <v>2</v>
       </c>
       <c r="F201" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -8952,7 +8952,7 @@
         <v>2</v>
       </c>
       <c r="F202" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -8972,7 +8972,7 @@
         <v>1</v>
       </c>
       <c r="F203" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -8992,7 +8992,7 @@
         <v>1</v>
       </c>
       <c r="F204" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -9012,7 +9012,7 @@
         <v>1</v>
       </c>
       <c r="F205" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -9032,7 +9032,7 @@
         <v>1</v>
       </c>
       <c r="F206" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -9052,7 +9052,7 @@
         <v>1</v>
       </c>
       <c r="F207" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -9072,7 +9072,7 @@
         <v>1</v>
       </c>
       <c r="F208" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
@@ -9092,7 +9092,7 @@
         <v>1</v>
       </c>
       <c r="F209" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
@@ -9112,7 +9112,7 @@
         <v>1</v>
       </c>
       <c r="F210" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
@@ -9132,10 +9132,10 @@
         <v>1</v>
       </c>
       <c r="F211" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J211" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -9155,10 +9155,10 @@
         <v>1</v>
       </c>
       <c r="F212" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J212" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -9178,10 +9178,10 @@
         <v>1</v>
       </c>
       <c r="F213" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J213" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -9201,10 +9201,10 @@
         <v>1</v>
       </c>
       <c r="F214" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J214" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
@@ -9224,10 +9224,10 @@
         <v>1</v>
       </c>
       <c r="F215" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J215" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
@@ -9247,10 +9247,10 @@
         <v>1</v>
       </c>
       <c r="F216" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J216" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -9270,10 +9270,10 @@
         <v>1</v>
       </c>
       <c r="F217" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J217" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -9293,10 +9293,10 @@
         <v>1</v>
       </c>
       <c r="F218" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J218" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -9316,10 +9316,10 @@
         <v>1</v>
       </c>
       <c r="F219" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J219" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
@@ -9339,10 +9339,10 @@
         <v>1</v>
       </c>
       <c r="F220" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J220" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -9362,10 +9362,10 @@
         <v>1</v>
       </c>
       <c r="F221" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
@@ -9385,10 +9385,10 @@
         <v>1</v>
       </c>
       <c r="F222" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J222" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
@@ -9408,10 +9408,10 @@
         <v>1</v>
       </c>
       <c r="F223" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J223" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
@@ -9431,10 +9431,10 @@
         <v>1</v>
       </c>
       <c r="F224" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J224" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -9454,10 +9454,10 @@
         <v>1</v>
       </c>
       <c r="F225" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J225" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
@@ -9477,10 +9477,10 @@
         <v>1</v>
       </c>
       <c r="F226" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J226" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
@@ -9500,10 +9500,10 @@
         <v>1</v>
       </c>
       <c r="F227" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J227" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
@@ -9523,10 +9523,10 @@
         <v>1</v>
       </c>
       <c r="F228" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J228" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
@@ -9546,10 +9546,10 @@
         <v>1</v>
       </c>
       <c r="F229" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J229" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
@@ -9569,7 +9569,7 @@
         <v>1</v>
       </c>
       <c r="F230" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
@@ -9589,12 +9589,12 @@
         <v>0</v>
       </c>
       <c r="F231" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B232">
         <v>21982</v>
@@ -9609,15 +9609,15 @@
         <v>1</v>
       </c>
       <c r="F232" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J232" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B233">
         <v>22216</v>
@@ -9632,15 +9632,15 @@
         <v>1</v>
       </c>
       <c r="F233" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J233" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B234">
         <v>22568</v>
@@ -9655,15 +9655,15 @@
         <v>1</v>
       </c>
       <c r="F234" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J234" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B235">
         <v>22792</v>
@@ -9678,15 +9678,15 @@
         <v>1</v>
       </c>
       <c r="F235" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J235" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B236">
         <v>25488</v>
@@ -9701,15 +9701,15 @@
         <v>1</v>
       </c>
       <c r="F236" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J236" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B237">
         <v>23363</v>
@@ -9724,12 +9724,12 @@
         <v>1</v>
       </c>
       <c r="F237" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B238">
         <v>23587</v>
@@ -9744,12 +9744,12 @@
         <v>1</v>
       </c>
       <c r="F238" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B239">
         <v>23391</v>
@@ -9764,12 +9764,12 @@
         <v>1</v>
       </c>
       <c r="F239" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B240">
         <v>23409</v>
@@ -9784,7 +9784,7 @@
         <v>2</v>
       </c>
       <c r="F240" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -9804,7 +9804,7 @@
         <v>1</v>
       </c>
       <c r="F241" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -9824,7 +9824,7 @@
         <v>1</v>
       </c>
       <c r="F242" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -9844,7 +9844,7 @@
         <v>1</v>
       </c>
       <c r="F243" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -9864,7 +9864,7 @@
         <v>1</v>
       </c>
       <c r="F244" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -9884,7 +9884,7 @@
         <v>1</v>
       </c>
       <c r="F245" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -9904,7 +9904,7 @@
         <v>2</v>
       </c>
       <c r="F246" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -9924,7 +9924,7 @@
         <v>2</v>
       </c>
       <c r="F247" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -9944,7 +9944,7 @@
         <v>1</v>
       </c>
       <c r="F248" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -9964,7 +9964,7 @@
         <v>1</v>
       </c>
       <c r="F249" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -9984,7 +9984,7 @@
         <v>1</v>
       </c>
       <c r="F250" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -10004,7 +10004,7 @@
         <v>1</v>
       </c>
       <c r="F251" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -10024,7 +10024,7 @@
         <v>1</v>
       </c>
       <c r="F252" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -10044,7 +10044,7 @@
         <v>1</v>
       </c>
       <c r="F253" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -10064,7 +10064,7 @@
         <v>1</v>
       </c>
       <c r="F254" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -10084,7 +10084,7 @@
         <v>1</v>
       </c>
       <c r="F255" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -10104,7 +10104,7 @@
         <v>1</v>
       </c>
       <c r="F256" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -10124,7 +10124,7 @@
         <v>1</v>
       </c>
       <c r="F257" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -10144,7 +10144,7 @@
         <v>1</v>
       </c>
       <c r="F258" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -10164,7 +10164,7 @@
         <v>1</v>
       </c>
       <c r="F259" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -10184,7 +10184,7 @@
         <v>1</v>
       </c>
       <c r="F260" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -10204,7 +10204,7 @@
         <v>1</v>
       </c>
       <c r="F261" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -10224,7 +10224,7 @@
         <v>1</v>
       </c>
       <c r="F262" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -10244,7 +10244,7 @@
         <v>1</v>
       </c>
       <c r="F263" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -10264,7 +10264,7 @@
         <v>1</v>
       </c>
       <c r="F264" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -10284,7 +10284,7 @@
         <v>1</v>
       </c>
       <c r="F265" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -10304,7 +10304,7 @@
         <v>1</v>
       </c>
       <c r="F266" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -10324,7 +10324,7 @@
         <v>1</v>
       </c>
       <c r="F267" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -10344,7 +10344,7 @@
         <v>1</v>
       </c>
       <c r="F268" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -10364,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="F269" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -10384,7 +10384,7 @@
         <v>1</v>
       </c>
       <c r="F270" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -10404,7 +10404,7 @@
         <v>1</v>
       </c>
       <c r="F271" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -10424,7 +10424,7 @@
         <v>1</v>
       </c>
       <c r="F272" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
@@ -10444,7 +10444,7 @@
         <v>1</v>
       </c>
       <c r="F273" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
@@ -10464,7 +10464,7 @@
         <v>1</v>
       </c>
       <c r="F274" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="F275" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
@@ -10504,7 +10504,7 @@
         <v>1</v>
       </c>
       <c r="F276" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
@@ -10524,7 +10524,7 @@
         <v>1</v>
       </c>
       <c r="F277" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
@@ -10544,7 +10544,7 @@
         <v>1</v>
       </c>
       <c r="F278" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
@@ -10564,7 +10564,7 @@
         <v>1</v>
       </c>
       <c r="F279" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
@@ -10584,7 +10584,7 @@
         <v>1</v>
       </c>
       <c r="F280" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
@@ -10604,7 +10604,7 @@
         <v>1</v>
       </c>
       <c r="F281" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.25">
@@ -10624,7 +10624,7 @@
         <v>1</v>
       </c>
       <c r="F282" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
@@ -10644,7 +10644,7 @@
         <v>1</v>
       </c>
       <c r="F283" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
@@ -10664,12 +10664,12 @@
         <v>1</v>
       </c>
       <c r="F284" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B285">
         <v>23059</v>
@@ -10684,15 +10684,15 @@
         <v>1</v>
       </c>
       <c r="F285" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J285" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B286">
         <v>23720</v>
@@ -10707,15 +10707,15 @@
         <v>1</v>
       </c>
       <c r="F286" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J286" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B287">
         <v>24001</v>
@@ -10730,15 +10730,15 @@
         <v>1</v>
       </c>
       <c r="F287" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J287" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B288">
         <v>26080</v>
@@ -10753,10 +10753,10 @@
         <v>1</v>
       </c>
       <c r="F288" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J288" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
@@ -10776,7 +10776,7 @@
         <v>1</v>
       </c>
       <c r="F289" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
@@ -10796,7 +10796,7 @@
         <v>1</v>
       </c>
       <c r="F290" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
@@ -10816,7 +10816,7 @@
         <v>1</v>
       </c>
       <c r="F291" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
@@ -10836,12 +10836,12 @@
         <v>1</v>
       </c>
       <c r="F292" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B293">
         <v>24608</v>
@@ -10856,15 +10856,15 @@
         <v>1</v>
       </c>
       <c r="F293" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J293" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B294">
         <v>24819</v>
@@ -10879,15 +10879,15 @@
         <v>1</v>
       </c>
       <c r="F294" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J294" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B295">
         <v>25096</v>
@@ -10902,15 +10902,15 @@
         <v>1</v>
       </c>
       <c r="F295" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J295" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B296">
         <v>25773</v>
@@ -10925,15 +10925,15 @@
         <v>1</v>
       </c>
       <c r="F296" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J296" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B297">
         <v>24448</v>
@@ -10948,10 +10948,10 @@
         <v>1</v>
       </c>
       <c r="F297" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J297" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
@@ -10971,7 +10971,7 @@
         <v>1</v>
       </c>
       <c r="F298" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
@@ -10991,7 +10991,7 @@
         <v>1</v>
       </c>
       <c r="F299" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
@@ -11011,7 +11011,7 @@
         <v>1</v>
       </c>
       <c r="F300" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
@@ -11031,7 +11031,7 @@
         <v>1</v>
       </c>
       <c r="F301" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.25">
@@ -11051,7 +11051,7 @@
         <v>1</v>
       </c>
       <c r="F302" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.25">
@@ -11071,7 +11071,7 @@
         <v>1</v>
       </c>
       <c r="F303" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.25">
@@ -11091,7 +11091,7 @@
         <v>1</v>
       </c>
       <c r="F304" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -11111,7 +11111,7 @@
         <v>2</v>
       </c>
       <c r="F305" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -11131,7 +11131,7 @@
         <v>2</v>
       </c>
       <c r="F306" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -11151,7 +11151,7 @@
         <v>1</v>
       </c>
       <c r="F307" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -11171,7 +11171,7 @@
         <v>1</v>
       </c>
       <c r="F308" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -11191,7 +11191,7 @@
         <v>1</v>
       </c>
       <c r="F309" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -11211,7 +11211,7 @@
         <v>1</v>
       </c>
       <c r="F310" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -11231,7 +11231,7 @@
         <v>2</v>
       </c>
       <c r="F311" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -11251,7 +11251,7 @@
         <v>2</v>
       </c>
       <c r="F312" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -11271,7 +11271,7 @@
         <v>1</v>
       </c>
       <c r="F313" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -11291,7 +11291,7 @@
         <v>1</v>
       </c>
       <c r="F314" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -11311,7 +11311,7 @@
         <v>1</v>
       </c>
       <c r="F315" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -11331,7 +11331,7 @@
         <v>1</v>
       </c>
       <c r="F316" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -11351,7 +11351,7 @@
         <v>1</v>
       </c>
       <c r="F317" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -11371,7 +11371,7 @@
         <v>1</v>
       </c>
       <c r="F318" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -11391,7 +11391,7 @@
         <v>2</v>
       </c>
       <c r="F319" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -11411,7 +11411,7 @@
         <v>2</v>
       </c>
       <c r="F320" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -11431,7 +11431,7 @@
         <v>2</v>
       </c>
       <c r="F321" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -11451,7 +11451,7 @@
         <v>2</v>
       </c>
       <c r="F322" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -11471,7 +11471,7 @@
         <v>2</v>
       </c>
       <c r="F323" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -11491,7 +11491,7 @@
         <v>2</v>
       </c>
       <c r="F324" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -11511,7 +11511,7 @@
         <v>1</v>
       </c>
       <c r="F325" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -11531,7 +11531,7 @@
         <v>2</v>
       </c>
       <c r="F326" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -11551,7 +11551,7 @@
         <v>1</v>
       </c>
       <c r="F327" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -11571,7 +11571,7 @@
         <v>1</v>
       </c>
       <c r="F328" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -11591,7 +11591,7 @@
         <v>1</v>
       </c>
       <c r="F329" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -11611,7 +11611,7 @@
         <v>1</v>
       </c>
       <c r="F330" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -11631,7 +11631,7 @@
         <v>3</v>
       </c>
       <c r="F331" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -11650,7 +11650,7 @@
   <sheetData>
     <row r="4" spans="2:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -11666,28 +11666,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" t="s">
         <v>222</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>223</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>224</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>225</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>226</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>227</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>228</v>
-      </c>
-      <c r="H1" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -13110,15 +13110,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" t="s">
         <v>213</v>
-      </c>
-      <c r="B1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B2" s="5">
         <v>45557</v>
@@ -13126,38 +13126,38 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" t="s">
         <v>217</v>
-      </c>
-      <c r="B4" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="66" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -13167,23 +13167,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="f82b70a8-9591-478e-a6d5-bf315b83c485" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100B01D25D17823C344A9D69518AF56DC62" ma:contentTypeVersion="6" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f29605d1c82d3d43c74cd3efc573dd15">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f82b70a8-9591-478e-a6d5-bf315b83c485" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d7d0483a01e3419b531383906934819f" ns3:_="">
     <xsd:import namespace="f82b70a8-9591-478e-a6d5-bf315b83c485"/>
@@ -13339,31 +13322,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFEF422C-B8D3-4F6C-950A-A4DFD4067B7B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="f82b70a8-9591-478e-a6d5-bf315b83c485"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80E8E46-C8F1-4EA0-9D75-58D6A3F6209E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="f82b70a8-9591-478e-a6d5-bf315b83c485" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3840DE93-E5DB-49F7-A595-E7AEB960EE63}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13379,4 +13355,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80E8E46-C8F1-4EA0-9D75-58D6A3F6209E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFEF422C-B8D3-4F6C-950A-A4DFD4067B7B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="f82b70a8-9591-478e-a6d5-bf315b83c485"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/src/zf_NG_brain_annotation_20240922.xlsx
+++ b/src/zf_NG_brain_annotation_20240922.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\其他電腦\My Computer\GlycoMSParser\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0617E8D2-DE93-4B0C-9A9A-81C8A9CB10D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FC7770-7175-4ADA-B0CB-22E20D3252CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7500" yWindow="2085" windowWidth="18450" windowHeight="10305" activeTab="1" xr2:uid="{CFD31651-57D7-40EF-BE95-C7417EC3B9A0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{CFD31651-57D7-40EF-BE95-C7417EC3B9A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Glycanlist" sheetId="2" r:id="rId1"/>
@@ -1013,7 +1013,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1452,7 +1452,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462C1F79-CAD9-4365-95EB-9CD91F872BD7}">
   <dimension ref="A1:S70"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="17.75" customWidth="1"/>
@@ -1462,7 +1462,7 @@
     <col min="15" max="15" width="38.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19">
       <c r="B2" t="s">
         <v>15</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>1.0072999999999865</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19">
       <c r="B4" t="s">
         <v>20</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19">
       <c r="B8" t="s">
         <v>62</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19">
       <c r="B9" t="s">
         <v>22</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19">
       <c r="A10" t="s">
         <v>73</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19">
       <c r="A12" t="s">
         <v>76</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19">
       <c r="B14" t="s">
         <v>24</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19">
       <c r="B15" t="s">
         <v>31</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>163</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15">
       <c r="B20" t="s">
         <v>26</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>169</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
         <v>87</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
         <v>90</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
         <v>92</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
         <v>94</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15">
       <c r="A31">
         <v>42</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
         <v>96</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
         <v>99</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
         <v>101</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15">
       <c r="A35">
         <v>52</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15">
       <c r="A36">
         <v>53</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
         <v>108</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15">
       <c r="A38">
         <v>57</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15">
       <c r="B39" t="s">
         <v>48</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15">
       <c r="A40">
         <v>58</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15">
       <c r="A41">
         <v>59</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15">
       <c r="A42">
         <v>60</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15">
       <c r="A43">
         <v>61</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
         <v>114</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15">
       <c r="A45">
         <v>65</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15">
       <c r="A46">
         <v>66</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15">
       <c r="A47" t="s">
         <v>119</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15">
       <c r="C48" t="s">
         <v>196</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15">
       <c r="C49" t="s">
         <v>121</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15">
       <c r="A50" t="s">
         <v>122</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15">
       <c r="C51" t="s">
         <v>124</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
         <v>125</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15">
       <c r="A53">
         <v>74</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15">
       <c r="A54" t="s">
         <v>129</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15">
       <c r="C55" t="s">
         <v>131</v>
       </c>
@@ -3945,7 +3945,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15">
       <c r="A56">
         <v>77</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15">
       <c r="A57">
         <v>78</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15">
       <c r="A58" t="s">
         <v>133</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15">
       <c r="A59">
         <v>81</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15">
       <c r="A61">
         <v>85</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15">
       <c r="A62">
         <v>86</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15">
       <c r="A63" t="s">
         <v>137</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15">
       <c r="A64">
         <v>89</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15">
       <c r="A65">
         <v>90</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15">
       <c r="A66">
         <v>91</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15">
       <c r="A67">
         <v>92</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15">
       <c r="A68">
         <v>93</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15">
       <c r="A69">
         <v>94</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15">
       <c r="A70">
         <v>95</v>
       </c>
@@ -4643,12 +4643,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE93C52-9AF5-4E67-9AF9-82CA7831A591}">
   <dimension ref="A1:J331"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>154</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>154</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>154</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>154</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>154</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>154</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>154</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>156</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>156</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>156</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>157</v>
       </c>
@@ -4900,7 +4900,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>157</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>158</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>158</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>158</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>158</v>
       </c>
@@ -5012,7 +5012,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>61</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>159</v>
       </c>
@@ -5115,7 +5115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>159</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>159</v>
       </c>
@@ -5161,7 +5161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>159</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>159</v>
       </c>
@@ -5207,7 +5207,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>63</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -5387,7 +5387,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>63</v>
       </c>
@@ -5407,7 +5407,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>63</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>63</v>
       </c>
@@ -5467,7 +5467,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -5490,7 +5490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -5513,7 +5513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>75</v>
       </c>
@@ -5556,7 +5556,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>75</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>75</v>
       </c>
@@ -5596,7 +5596,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>75</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -5636,7 +5636,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>75</v>
       </c>
@@ -5656,7 +5656,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>75</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -5696,7 +5696,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>75</v>
       </c>
@@ -5716,7 +5716,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>77</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>77</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -5796,7 +5796,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>77</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>77</v>
       </c>
@@ -5836,7 +5836,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>77</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>79</v>
       </c>
@@ -5876,7 +5876,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>79</v>
       </c>
@@ -5896,7 +5896,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>79</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>79</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>79</v>
       </c>
@@ -5956,7 +5956,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>79</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>79</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>79</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>79</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>79</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>79</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -6096,7 +6096,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>79</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>81</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>81</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>81</v>
       </c>
@@ -6231,7 +6231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>81</v>
       </c>
@@ -6300,7 +6300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10">
       <c r="A81" t="s">
         <v>81</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10">
       <c r="A82" t="s">
         <v>39</v>
       </c>
@@ -6369,7 +6369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10">
       <c r="A83" t="s">
         <v>39</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -6415,7 +6415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10">
       <c r="A85" t="s">
         <v>39</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10">
       <c r="A86" t="s">
         <v>39</v>
       </c>
@@ -6461,7 +6461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10">
       <c r="A87" t="s">
         <v>39</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10">
       <c r="A89" t="s">
         <v>39</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10">
       <c r="A90" t="s">
         <v>39</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10">
       <c r="A92" t="s">
         <v>39</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10">
       <c r="A93" t="s">
         <v>26</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10">
       <c r="A94" t="s">
         <v>26</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10">
       <c r="A95" t="s">
         <v>26</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10">
       <c r="A96" t="s">
         <v>26</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>36</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>36</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>36</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>36</v>
       </c>
@@ -6765,7 +6765,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>36</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>36</v>
       </c>
@@ -6805,7 +6805,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>84</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>84</v>
       </c>
@@ -6845,7 +6845,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>84</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>84</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>84</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>84</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>84</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>84</v>
       </c>
@@ -6965,7 +6965,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>84</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>84</v>
       </c>
@@ -7005,7 +7005,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10">
       <c r="A113" t="s">
         <v>84</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10">
       <c r="A114" t="s">
         <v>84</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10">
       <c r="A115" t="s">
         <v>84</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10">
       <c r="A116" t="s">
         <v>58</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10">
       <c r="A117" t="s">
         <v>58</v>
       </c>
@@ -7108,7 +7108,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10">
       <c r="A118" t="s">
         <v>89</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10">
       <c r="A119" t="s">
         <v>89</v>
       </c>
@@ -7160,7 +7160,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10">
       <c r="A120" t="s">
         <v>89</v>
       </c>
@@ -7183,7 +7183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10">
       <c r="A121" t="s">
         <v>89</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10">
       <c r="A122" t="s">
         <v>89</v>
       </c>
@@ -7229,7 +7229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10">
       <c r="A123" t="s">
         <v>89</v>
       </c>
@@ -7252,7 +7252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10">
       <c r="A124" t="s">
         <v>89</v>
       </c>
@@ -7275,7 +7275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10">
       <c r="A125" t="s">
         <v>89</v>
       </c>
@@ -7298,7 +7298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10">
       <c r="A126" t="s">
         <v>89</v>
       </c>
@@ -7321,7 +7321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10">
       <c r="A127" t="s">
         <v>89</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10">
       <c r="A128" t="s">
         <v>89</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10">
       <c r="A129" t="s">
         <v>89</v>
       </c>
@@ -7390,7 +7390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10">
       <c r="A130" t="s">
         <v>89</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10">
       <c r="A131" t="s">
         <v>89</v>
       </c>
@@ -7436,7 +7436,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10">
       <c r="A132" t="s">
         <v>89</v>
       </c>
@@ -7459,7 +7459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10">
       <c r="A133" t="s">
         <v>89</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10">
       <c r="A134" t="s">
         <v>93</v>
       </c>
@@ -7505,7 +7505,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10">
       <c r="A135" t="s">
         <v>93</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10">
       <c r="A136" t="s">
         <v>93</v>
       </c>
@@ -7545,7 +7545,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10">
       <c r="A137" t="s">
         <v>93</v>
       </c>
@@ -7565,7 +7565,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10">
       <c r="A138" t="s">
         <v>177</v>
       </c>
@@ -7588,7 +7588,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10">
       <c r="A139" t="s">
         <v>177</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10">
       <c r="A140" t="s">
         <v>177</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10">
       <c r="A141" t="s">
         <v>177</v>
       </c>
@@ -7657,7 +7657,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10">
       <c r="A142" t="s">
         <v>177</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10">
       <c r="A143" t="s">
         <v>177</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10">
       <c r="A144" t="s">
         <v>177</v>
       </c>
@@ -7726,7 +7726,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10">
       <c r="A145" t="s">
         <v>177</v>
       </c>
@@ -7749,7 +7749,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10">
       <c r="A146" t="s">
         <v>177</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10">
       <c r="A147" t="s">
         <v>100</v>
       </c>
@@ -7798,7 +7798,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10">
       <c r="A148" t="s">
         <v>100</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10">
       <c r="A149" t="s">
         <v>100</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10">
       <c r="A150" t="s">
         <v>100</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10">
       <c r="A151" t="s">
         <v>100</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10">
       <c r="A152" t="s">
         <v>100</v>
       </c>
@@ -7919,7 +7919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10">
       <c r="A153" t="s">
         <v>100</v>
       </c>
@@ -7942,7 +7942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10">
       <c r="A154" t="s">
         <v>100</v>
       </c>
@@ -7965,7 +7965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10">
       <c r="A155" t="s">
         <v>100</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10">
       <c r="A156" t="s">
         <v>100</v>
       </c>
@@ -8014,7 +8014,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10">
       <c r="A157" t="s">
         <v>100</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10">
       <c r="A158" t="s">
         <v>100</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10">
       <c r="A159" t="s">
         <v>100</v>
       </c>
@@ -8086,7 +8086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10">
       <c r="A160" t="s">
         <v>100</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10">
       <c r="A161" t="s">
         <v>100</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10">
       <c r="A162" t="s">
         <v>183</v>
       </c>
@@ -8155,7 +8155,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10">
       <c r="A163" t="s">
         <v>183</v>
       </c>
@@ -8175,7 +8175,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10">
       <c r="A164" t="s">
         <v>183</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10">
       <c r="A165" t="s">
         <v>183</v>
       </c>
@@ -8215,7 +8215,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10">
       <c r="A166" t="s">
         <v>183</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10">
       <c r="A167" t="s">
         <v>183</v>
       </c>
@@ -8255,7 +8255,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10">
       <c r="A168" t="s">
         <v>183</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10">
       <c r="A169" t="s">
         <v>183</v>
       </c>
@@ -8295,7 +8295,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10">
       <c r="A170" t="s">
         <v>183</v>
       </c>
@@ -8315,7 +8315,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10">
       <c r="A171" t="s">
         <v>183</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10">
       <c r="A172" t="s">
         <v>183</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10">
       <c r="A173" t="s">
         <v>109</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10">
       <c r="A174" t="s">
         <v>109</v>
       </c>
@@ -8395,7 +8395,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10">
       <c r="A175" t="s">
         <v>109</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10">
       <c r="A176" t="s">
         <v>109</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>109</v>
       </c>
@@ -8455,7 +8455,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6">
       <c r="A178" t="s">
         <v>186</v>
       </c>
@@ -8475,7 +8475,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>186</v>
       </c>
@@ -8495,7 +8495,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>186</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>186</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>186</v>
       </c>
@@ -8555,7 +8555,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
         <v>186</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6">
       <c r="A184" t="s">
         <v>111</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6">
       <c r="A185" t="s">
         <v>111</v>
       </c>
@@ -8615,7 +8615,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6">
       <c r="A186" t="s">
         <v>111</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6">
       <c r="A187" t="s">
         <v>111</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6">
       <c r="A188" t="s">
         <v>111</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6">
       <c r="A189" t="s">
         <v>111</v>
       </c>
@@ -8695,7 +8695,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6">
       <c r="A190" t="s">
         <v>111</v>
       </c>
@@ -8715,7 +8715,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6">
       <c r="A191" t="s">
         <v>111</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6">
       <c r="A192" t="s">
         <v>111</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>111</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6">
       <c r="A194" t="s">
         <v>111</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>111</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>111</v>
       </c>
@@ -8835,7 +8835,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6">
       <c r="A197" t="s">
         <v>111</v>
       </c>
@@ -8855,7 +8855,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6">
       <c r="A198" t="s">
         <v>111</v>
       </c>
@@ -8875,7 +8875,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6">
       <c r="A199" t="s">
         <v>111</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6">
       <c r="A200" t="s">
         <v>111</v>
       </c>
@@ -8915,7 +8915,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>111</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>111</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>111</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6">
       <c r="A204" t="s">
         <v>111</v>
       </c>
@@ -8995,7 +8995,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6">
       <c r="A205" t="s">
         <v>111</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6">
       <c r="A206" t="s">
         <v>111</v>
       </c>
@@ -9035,7 +9035,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6">
       <c r="A207" t="s">
         <v>111</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>111</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10">
       <c r="A209" t="s">
         <v>111</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10">
       <c r="A210" t="s">
         <v>111</v>
       </c>
@@ -9115,7 +9115,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10">
       <c r="A211" t="s">
         <v>116</v>
       </c>
@@ -9138,7 +9138,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10">
       <c r="A212" t="s">
         <v>116</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10">
       <c r="A213" t="s">
         <v>116</v>
       </c>
@@ -9184,7 +9184,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10">
       <c r="A214" t="s">
         <v>116</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10">
       <c r="A215" t="s">
         <v>116</v>
       </c>
@@ -9230,7 +9230,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10">
       <c r="A216" t="s">
         <v>116</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10">
       <c r="A217" t="s">
         <v>116</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10">
       <c r="A218" t="s">
         <v>116</v>
       </c>
@@ -9299,7 +9299,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10">
       <c r="A219" t="s">
         <v>116</v>
       </c>
@@ -9322,7 +9322,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10">
       <c r="A220" t="s">
         <v>116</v>
       </c>
@@ -9345,7 +9345,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10">
       <c r="A221" t="s">
         <v>116</v>
       </c>
@@ -9368,7 +9368,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10">
       <c r="A222" t="s">
         <v>116</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10">
       <c r="A223" t="s">
         <v>116</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10">
       <c r="A224" t="s">
         <v>116</v>
       </c>
@@ -9437,7 +9437,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10">
       <c r="A225" t="s">
         <v>116</v>
       </c>
@@ -9460,7 +9460,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10">
       <c r="A226" t="s">
         <v>116</v>
       </c>
@@ -9483,7 +9483,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10">
       <c r="A227" t="s">
         <v>116</v>
       </c>
@@ -9506,7 +9506,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10">
       <c r="A228" t="s">
         <v>116</v>
       </c>
@@ -9529,7 +9529,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10">
       <c r="A229" t="s">
         <v>116</v>
       </c>
@@ -9552,7 +9552,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10">
       <c r="A230" t="s">
         <v>117</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10">
       <c r="A231" t="s">
         <v>117</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10">
       <c r="A232" t="s">
         <v>192</v>
       </c>
@@ -9615,7 +9615,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10">
       <c r="A233" t="s">
         <v>192</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10">
       <c r="A234" t="s">
         <v>192</v>
       </c>
@@ -9661,7 +9661,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10">
       <c r="A235" t="s">
         <v>192</v>
       </c>
@@ -9684,7 +9684,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10">
       <c r="A236" t="s">
         <v>192</v>
       </c>
@@ -9707,7 +9707,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10">
       <c r="A237" t="s">
         <v>196</v>
       </c>
@@ -9727,7 +9727,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10">
       <c r="A238" t="s">
         <v>196</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10">
       <c r="A239" t="s">
         <v>196</v>
       </c>
@@ -9767,7 +9767,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10">
       <c r="A240" t="s">
         <v>196</v>
       </c>
@@ -9787,7 +9787,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6">
       <c r="A241" t="s">
         <v>123</v>
       </c>
@@ -9807,7 +9807,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6">
       <c r="A242" t="s">
         <v>123</v>
       </c>
@@ -9827,7 +9827,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6">
       <c r="A243" t="s">
         <v>123</v>
       </c>
@@ -9847,7 +9847,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6">
       <c r="A244" t="s">
         <v>123</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6">
       <c r="A245" t="s">
         <v>123</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6">
       <c r="A246" t="s">
         <v>123</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6">
       <c r="A247" t="s">
         <v>123</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6">
       <c r="A248" t="s">
         <v>130</v>
       </c>
@@ -9947,7 +9947,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6">
       <c r="A249" t="s">
         <v>130</v>
       </c>
@@ -9967,7 +9967,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6">
       <c r="A250" t="s">
         <v>130</v>
       </c>
@@ -9987,7 +9987,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6">
       <c r="A251" t="s">
         <v>130</v>
       </c>
@@ -10007,7 +10007,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6">
       <c r="A252" t="s">
         <v>130</v>
       </c>
@@ -10027,7 +10027,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6">
       <c r="A253" t="s">
         <v>130</v>
       </c>
@@ -10047,7 +10047,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6">
       <c r="A254" t="s">
         <v>130</v>
       </c>
@@ -10067,7 +10067,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6">
       <c r="A255" t="s">
         <v>130</v>
       </c>
@@ -10087,7 +10087,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6">
       <c r="A256" t="s">
         <v>130</v>
       </c>
@@ -10107,7 +10107,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>130</v>
       </c>
@@ -10127,7 +10127,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>130</v>
       </c>
@@ -10147,7 +10147,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>130</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>130</v>
       </c>
@@ -10187,7 +10187,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>130</v>
       </c>
@@ -10207,7 +10207,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>130</v>
       </c>
@@ -10227,7 +10227,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>130</v>
       </c>
@@ -10247,7 +10247,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>130</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>130</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>130</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>130</v>
       </c>
@@ -10327,7 +10327,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>51</v>
       </c>
@@ -10347,7 +10347,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>51</v>
       </c>
@@ -10367,7 +10367,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>51</v>
       </c>
@@ -10387,7 +10387,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>51</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>51</v>
       </c>
@@ -10427,7 +10427,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10">
       <c r="A273" t="s">
         <v>51</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10">
       <c r="A274" t="s">
         <v>51</v>
       </c>
@@ -10467,7 +10467,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10">
       <c r="A275" t="s">
         <v>51</v>
       </c>
@@ -10487,7 +10487,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10">
       <c r="A276" t="s">
         <v>51</v>
       </c>
@@ -10507,7 +10507,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10">
       <c r="A277" t="s">
         <v>51</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10">
       <c r="A278" t="s">
         <v>51</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10">
       <c r="A279" t="s">
         <v>51</v>
       </c>
@@ -10567,7 +10567,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10">
       <c r="A280" t="s">
         <v>51</v>
       </c>
@@ -10587,7 +10587,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10">
       <c r="A281" t="s">
         <v>135</v>
       </c>
@@ -10607,7 +10607,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10">
       <c r="A282" t="s">
         <v>135</v>
       </c>
@@ -10627,7 +10627,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10">
       <c r="A283" t="s">
         <v>135</v>
       </c>
@@ -10647,7 +10647,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10">
       <c r="A284" t="s">
         <v>135</v>
       </c>
@@ -10667,7 +10667,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10">
       <c r="A285" t="s">
         <v>203</v>
       </c>
@@ -10690,7 +10690,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10">
       <c r="A286" t="s">
         <v>203</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10">
       <c r="A287" t="s">
         <v>203</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10">
       <c r="A288" t="s">
         <v>203</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10">
       <c r="A289" t="s">
         <v>66</v>
       </c>
@@ -10779,7 +10779,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10">
       <c r="A290" t="s">
         <v>66</v>
       </c>
@@ -10799,7 +10799,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10">
       <c r="A291" t="s">
         <v>66</v>
       </c>
@@ -10819,7 +10819,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10">
       <c r="A292" t="s">
         <v>66</v>
       </c>
@@ -10839,7 +10839,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10">
       <c r="A293" t="s">
         <v>207</v>
       </c>
@@ -10862,7 +10862,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10">
       <c r="A294" t="s">
         <v>207</v>
       </c>
@@ -10885,7 +10885,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10">
       <c r="A295" t="s">
         <v>207</v>
       </c>
@@ -10908,7 +10908,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10">
       <c r="A296" t="s">
         <v>207</v>
       </c>
@@ -10931,7 +10931,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10">
       <c r="A297" t="s">
         <v>207</v>
       </c>
@@ -10954,7 +10954,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10">
       <c r="A298" t="s">
         <v>136</v>
       </c>
@@ -10974,7 +10974,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10">
       <c r="A299" t="s">
         <v>136</v>
       </c>
@@ -10994,7 +10994,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10">
       <c r="A300" t="s">
         <v>136</v>
       </c>
@@ -11014,7 +11014,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10">
       <c r="A301" t="s">
         <v>136</v>
       </c>
@@ -11034,7 +11034,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10">
       <c r="A302" t="s">
         <v>138</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10">
       <c r="A303" t="s">
         <v>138</v>
       </c>
@@ -11074,7 +11074,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10">
       <c r="A304" t="s">
         <v>138</v>
       </c>
@@ -11094,7 +11094,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6">
       <c r="A305" t="s">
         <v>138</v>
       </c>
@@ -11114,7 +11114,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6">
       <c r="A306" t="s">
         <v>138</v>
       </c>
@@ -11134,7 +11134,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6">
       <c r="A307" t="s">
         <v>138</v>
       </c>
@@ -11154,7 +11154,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6">
       <c r="A308" t="s">
         <v>138</v>
       </c>
@@ -11174,7 +11174,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6">
       <c r="A309" t="s">
         <v>138</v>
       </c>
@@ -11194,7 +11194,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6">
       <c r="A310" t="s">
         <v>138</v>
       </c>
@@ -11214,7 +11214,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6">
       <c r="A311" t="s">
         <v>138</v>
       </c>
@@ -11234,7 +11234,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6">
       <c r="A312" t="s">
         <v>138</v>
       </c>
@@ -11254,7 +11254,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6">
       <c r="A313" t="s">
         <v>54</v>
       </c>
@@ -11274,7 +11274,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6">
       <c r="A314" t="s">
         <v>54</v>
       </c>
@@ -11294,7 +11294,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6">
       <c r="A315" t="s">
         <v>54</v>
       </c>
@@ -11314,7 +11314,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6">
       <c r="A316" t="s">
         <v>54</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6">
       <c r="A317" t="s">
         <v>54</v>
       </c>
@@ -11354,7 +11354,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6">
       <c r="A318" t="s">
         <v>54</v>
       </c>
@@ -11374,7 +11374,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6">
       <c r="A319" t="s">
         <v>54</v>
       </c>
@@ -11394,7 +11394,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6">
       <c r="A320" t="s">
         <v>54</v>
       </c>
@@ -11414,7 +11414,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6">
       <c r="A321" t="s">
         <v>54</v>
       </c>
@@ -11434,7 +11434,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6">
       <c r="A322" t="s">
         <v>54</v>
       </c>
@@ -11454,7 +11454,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6">
       <c r="A323" t="s">
         <v>54</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6">
       <c r="A324" t="s">
         <v>54</v>
       </c>
@@ -11494,7 +11494,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6">
       <c r="A325" t="s">
         <v>55</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6">
       <c r="A326" t="s">
         <v>55</v>
       </c>
@@ -11534,7 +11534,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6">
       <c r="A327" s="2" t="s">
         <v>56</v>
       </c>
@@ -11554,7 +11554,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6">
       <c r="A328" s="2" t="s">
         <v>56</v>
       </c>
@@ -11574,7 +11574,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6">
       <c r="A329" s="2" t="s">
         <v>56</v>
       </c>
@@ -11594,7 +11594,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6">
       <c r="A330" s="2" t="s">
         <v>56</v>
       </c>
@@ -11614,7 +11614,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6">
       <c r="A331" t="s">
         <v>142</v>
       </c>
@@ -11646,9 +11646,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98BDEB04-0D24-401D-B836-1BAABA03E8E4}">
   <dimension ref="B4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="4" spans="2:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:2" ht="409.5">
       <c r="B4" s="4" t="s">
         <v>173</v>
       </c>
@@ -11662,9 +11662,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D125B437-E159-4E97-8559-08AC52B2F723}">
   <dimension ref="A1:H281"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>221</v>
       </c>
@@ -11690,1402 +11690,1402 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="C2">
         <v>189.1121</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="C3">
         <v>205.1071</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="C4">
         <v>219.12270000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="C5">
         <v>246.1336</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="C6">
         <v>260.14920000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="C7">
         <v>264.14420000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="C8">
         <v>278.15980000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="C9">
         <v>344.17039999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="C10">
         <v>374.18099999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="C11">
         <v>376.19659999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="C12">
         <v>406.2072</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="C13">
         <v>409.20679999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="C14">
         <v>420.22280000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="C15">
         <v>423.22250000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="C16">
         <v>450.23340000000002</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3">
       <c r="C17">
         <v>452.24900000000002</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:3">
       <c r="C18">
         <v>464.24900000000002</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:3">
       <c r="C19">
         <v>509.27050000000003</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:3">
       <c r="C20">
         <v>523.28610000000003</v>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:3">
       <c r="C21">
         <v>566.28070000000002</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:3">
       <c r="C22">
         <v>580.29639999999995</v>
       </c>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:3">
       <c r="C23">
         <v>596.29129999999998</v>
       </c>
     </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:3">
       <c r="C24">
         <v>624.32259999999997</v>
       </c>
     </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:3">
       <c r="C25">
         <v>638.33820000000003</v>
       </c>
     </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:3">
       <c r="C26">
         <v>654.33309999999994</v>
       </c>
     </row>
-    <row r="27" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:3">
       <c r="C27">
         <v>668.34879999999998</v>
       </c>
     </row>
-    <row r="28" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:3">
       <c r="C28">
         <v>697.37530000000004</v>
       </c>
     </row>
-    <row r="29" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:3">
       <c r="C29">
         <v>713.37030000000004</v>
       </c>
     </row>
-    <row r="30" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:3">
       <c r="C30">
         <v>755.89099999999996</v>
       </c>
     </row>
-    <row r="31" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:3">
       <c r="C31">
         <v>756.38300000000004</v>
       </c>
     </row>
-    <row r="32" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:3">
       <c r="C32">
         <v>770.8963</v>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:3">
       <c r="C33">
         <v>776.8963</v>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:3">
       <c r="C34">
         <v>777.90409999999997</v>
       </c>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:3">
       <c r="C35">
         <v>784.39670000000001</v>
       </c>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:3">
       <c r="C36">
         <v>785.90160000000003</v>
       </c>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:3">
       <c r="C37">
         <v>793.39660000000003</v>
       </c>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:3">
       <c r="C38">
         <v>798.41740000000004</v>
       </c>
     </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:3">
       <c r="C39">
         <v>799.40139999999997</v>
       </c>
     </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:3">
       <c r="C40">
         <v>804.41740000000004</v>
       </c>
     </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:3">
       <c r="C41">
         <v>806.41489999999999</v>
       </c>
     </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:3">
       <c r="C42">
         <v>811.40700000000004</v>
       </c>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:3">
       <c r="C43" s="6">
         <v>814.4067</v>
       </c>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:3">
       <c r="C44">
         <v>825.42269999999996</v>
       </c>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:3">
       <c r="C45">
         <v>828.42240000000004</v>
       </c>
     </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:3">
       <c r="C46">
         <v>834.92</v>
       </c>
     </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:3">
       <c r="C47">
         <v>842.43799999999999</v>
       </c>
     </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:3">
       <c r="C48">
         <v>843.42759999999998</v>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:3">
       <c r="C49">
         <v>850.43550000000005</v>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:3">
       <c r="C50">
         <v>857.94090000000006</v>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:3">
       <c r="C51" s="6">
         <v>858.43290000000002</v>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:3">
       <c r="C52">
         <v>863.94090000000006</v>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:3">
       <c r="C53">
         <v>864.43849999999998</v>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:3">
       <c r="C54">
         <v>864.94870000000003</v>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:3">
       <c r="C55">
         <v>871.44640000000004</v>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:3">
       <c r="C56">
         <v>872.44860000000006</v>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:3">
       <c r="C57">
         <v>872.94619999999998</v>
       </c>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:3">
       <c r="C58">
         <v>878.94619999999998</v>
       </c>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:3">
       <c r="C59">
         <v>879.95399999999995</v>
       </c>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:3">
       <c r="C60">
         <v>887.45950000000005</v>
       </c>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:3">
       <c r="C61">
         <v>887.95150000000001</v>
       </c>
     </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:3">
       <c r="C62">
         <v>893.45950000000005</v>
       </c>
     </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:3">
       <c r="C63">
         <v>899.45950000000005</v>
       </c>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:3">
       <c r="C64">
         <v>900.46730000000002</v>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:3">
       <c r="C65">
         <v>901.45129999999995</v>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:3">
       <c r="C66">
         <v>908.46479999999997</v>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:3">
       <c r="C67">
         <v>916.45659999999998</v>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:3">
       <c r="C68">
         <v>917.47</v>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:3">
       <c r="C69">
         <v>921.96460000000002</v>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:3">
       <c r="C70">
         <v>935.98590000000002</v>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:3">
       <c r="C71">
         <v>936.96990000000005</v>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:3">
       <c r="C72">
         <v>943.97770000000003</v>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:3">
       <c r="C73">
         <v>945.47749999999996</v>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:3">
       <c r="C74">
         <v>951.48310000000004</v>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:3">
       <c r="C75">
         <v>957.48310000000004</v>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:3">
       <c r="C76">
         <v>958.49099999999999</v>
       </c>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:3">
       <c r="C77">
         <v>959.99080000000004</v>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:3">
       <c r="C78">
         <v>965.99080000000004</v>
       </c>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:3">
       <c r="C79">
         <v>966.48839999999996</v>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:3">
       <c r="C80">
         <v>966.99860000000001</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:3">
       <c r="C81">
         <v>972.99860000000001</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:3">
       <c r="C82">
         <v>973.49620000000004</v>
       </c>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:3">
       <c r="C83">
         <v>974.99609999999996</v>
       </c>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:3">
       <c r="C84">
         <v>980.50409999999999</v>
       </c>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:3">
       <c r="C85">
         <v>980.99609999999996</v>
       </c>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:3">
       <c r="C86">
         <v>981.49369999999999</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:3">
       <c r="C87">
         <v>982.00390000000004</v>
       </c>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:3">
       <c r="C88">
         <v>985.49620000000004</v>
       </c>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:3">
       <c r="C89">
         <v>995.50940000000003</v>
       </c>
     </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:3">
       <c r="C90">
         <v>1002.5172</v>
       </c>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:3">
       <c r="C91">
         <v>1010.5146</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:3">
       <c r="C92">
         <v>1015.5068</v>
       </c>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:3">
       <c r="C93">
         <v>1024.0145</v>
       </c>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:3">
       <c r="C94">
         <v>1029.5225</v>
       </c>
     </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:3">
       <c r="C95">
         <v>1030.0382999999999</v>
       </c>
     </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:3">
       <c r="C96">
         <v>1032.5220999999999</v>
       </c>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:3">
       <c r="C97">
         <v>1039.0198</v>
       </c>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:3">
       <c r="C98">
         <v>1044.5277000000001</v>
       </c>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:3">
       <c r="C99">
         <v>1045.5174</v>
       </c>
     </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:3">
       <c r="C100">
         <v>1046.0275999999999</v>
       </c>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:3">
       <c r="C101">
         <v>1053.5329999999999</v>
       </c>
     </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:3">
       <c r="C102">
         <v>1059.5329999999999</v>
       </c>
     </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:3">
       <c r="C103">
         <v>1060.5409</v>
       </c>
     </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:3">
       <c r="C104">
         <v>1062.5327</v>
       </c>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:3">
       <c r="C105">
         <v>1066.5409</v>
       </c>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:3">
       <c r="C106">
         <v>1068.0407</v>
       </c>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:3">
       <c r="C107">
         <v>1068.5382999999999</v>
       </c>
     </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:3">
       <c r="C108">
         <v>1069.0485000000001</v>
       </c>
     </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:3">
       <c r="C109">
         <v>1075.5461</v>
       </c>
     </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:3">
       <c r="C110">
         <v>1082.5540000000001</v>
       </c>
     </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:3">
       <c r="C111">
         <v>1083.5436</v>
       </c>
     </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:3">
       <c r="C112">
         <v>1089.0516</v>
       </c>
     </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:3">
       <c r="C113">
         <v>1091.5591999999999</v>
       </c>
     </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:3">
       <c r="C114">
         <v>1097.5591999999999</v>
       </c>
     </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:3">
       <c r="C115">
         <v>1103.5591999999999</v>
       </c>
     </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:3">
       <c r="C116">
         <v>1104.5671</v>
       </c>
     </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:3">
       <c r="C117">
         <v>1111.0590999999999</v>
       </c>
     </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:3">
       <c r="C118">
         <v>1112.5645</v>
       </c>
     </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:3">
       <c r="C119">
         <v>1117.5567000000001</v>
       </c>
     </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:3">
       <c r="C120">
         <v>1121.5698</v>
       </c>
     </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:3">
       <c r="C121">
         <v>1124.5645</v>
       </c>
     </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:3">
       <c r="C122">
         <v>1126.5907</v>
       </c>
     </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:3">
       <c r="C123">
         <v>1132.5858000000001</v>
       </c>
     </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:3">
       <c r="C124">
         <v>1133.0722000000001</v>
       </c>
     </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:3">
       <c r="C125">
         <v>1141.0696</v>
       </c>
     </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:3">
       <c r="C126">
         <v>1144.5858000000001</v>
       </c>
     </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:3">
       <c r="C127">
         <v>1146.5776000000001</v>
       </c>
     </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:3">
       <c r="C128">
         <v>1161.5829000000001</v>
       </c>
     </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:3">
       <c r="C129">
         <v>1162.5907</v>
       </c>
     </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:3">
       <c r="C130">
         <v>1162.5963999999999</v>
       </c>
     </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:3">
       <c r="C131">
         <v>1168.5907</v>
       </c>
     </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:3">
       <c r="C132">
         <v>1176.0962</v>
       </c>
     </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:3">
       <c r="C133">
         <v>1177.596</v>
       </c>
     </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:3">
       <c r="C134">
         <v>1183.104</v>
       </c>
     </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:3">
       <c r="C135">
         <v>1184.6038000000001</v>
       </c>
     </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:3">
       <c r="C136">
         <v>1189.596</v>
       </c>
     </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:3">
       <c r="C137">
         <v>1191.1015</v>
       </c>
     </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:3">
       <c r="C138">
         <v>1191.6116999999999</v>
       </c>
     </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:3">
       <c r="C139">
         <v>1198.1093000000001</v>
       </c>
     </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:3">
       <c r="C140">
         <v>1198.6195</v>
       </c>
     </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:3">
       <c r="C141">
         <v>1199.6090999999999</v>
       </c>
     </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:3">
       <c r="C142">
         <v>1203.6116999999999</v>
       </c>
     </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:3">
       <c r="C143">
         <v>1206.617</v>
       </c>
     </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:3">
       <c r="C144" s="6">
         <v>1219.6066000000001</v>
       </c>
     </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:3">
       <c r="C145">
         <v>1226.6143999999999</v>
       </c>
     </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:3">
       <c r="C146" s="6">
         <v>1233.6222</v>
       </c>
     </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:3">
       <c r="C147">
         <v>1236.6219000000001</v>
       </c>
     </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:3">
       <c r="C148">
         <v>1240.1198999999999</v>
       </c>
     </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:3">
       <c r="C149">
         <v>1247.1277</v>
       </c>
     </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:3">
       <c r="C150">
         <v>1248.6275000000001</v>
       </c>
     </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:3">
       <c r="C151">
         <v>1249.6171999999999</v>
       </c>
     </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:3">
       <c r="C152">
         <v>1255.6352999999999</v>
       </c>
     </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:3">
       <c r="C153">
         <v>1263.1407999999999</v>
       </c>
     </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:3">
       <c r="C154">
         <v>1263.6328000000001</v>
       </c>
     </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:3">
       <c r="C155">
         <v>1266.6324999999999</v>
       </c>
     </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:3">
       <c r="C156">
         <v>1270.1486</v>
       </c>
     </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:3">
       <c r="C157">
         <v>1277.6485</v>
       </c>
     </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:3">
       <c r="C158">
         <v>1278.1460999999999</v>
       </c>
     </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:3">
       <c r="C159">
         <v>1285.1539</v>
       </c>
     </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:3">
       <c r="C160">
         <v>1292.1617000000001</v>
       </c>
     </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:3">
       <c r="C161">
         <v>1293.1514</v>
       </c>
     </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:3">
       <c r="C162">
         <v>1293.6615999999999</v>
       </c>
     </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:3">
       <c r="C163">
         <v>1295.6590000000001</v>
       </c>
     </row>
-    <row r="164" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:3">
       <c r="C164">
         <v>1300.1592000000001</v>
       </c>
     </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:3">
       <c r="C165">
         <v>1301.6590000000001</v>
       </c>
     </row>
-    <row r="166" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:3">
       <c r="C166">
         <v>1307.6590000000001</v>
       </c>
     </row>
-    <row r="167" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:3">
       <c r="C167">
         <v>1315.1587999999999</v>
       </c>
     </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:3">
       <c r="C168">
         <v>1328.6642999999999</v>
       </c>
     </row>
-    <row r="169" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:3">
       <c r="C169">
         <v>1330.1641</v>
       </c>
     </row>
-    <row r="170" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:3">
       <c r="C170">
         <v>1336.6856</v>
       </c>
     </row>
-    <row r="171" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:3">
       <c r="C171">
         <v>1342.1696999999999</v>
       </c>
     </row>
-    <row r="172" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:3">
       <c r="C172">
         <v>1348.6856</v>
       </c>
     </row>
-    <row r="173" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:3">
       <c r="C173">
         <v>1349.1776</v>
       </c>
     </row>
-    <row r="174" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:3">
       <c r="C174">
         <v>1362.7012</v>
       </c>
     </row>
-    <row r="175" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:3">
       <c r="C175">
         <v>1366.6960999999999</v>
       </c>
     </row>
-    <row r="176" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:3">
       <c r="C176">
         <v>1371.6883</v>
       </c>
     </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="3:3">
       <c r="C177">
         <v>1372.1985</v>
       </c>
     </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="3:3">
       <c r="C178">
         <v>1378.6960999999999</v>
       </c>
     </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="3:3">
       <c r="C179">
         <v>1380.1959999999999</v>
       </c>
     </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="3:3">
       <c r="C180">
         <v>1387.2038</v>
       </c>
     </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:3">
       <c r="C181">
         <v>1388.7036000000001</v>
       </c>
     </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="3:3">
       <c r="C182">
         <v>1393.6958</v>
       </c>
     </row>
-    <row r="183" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="3:3">
       <c r="C183">
         <v>1394.2116000000001</v>
       </c>
     </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="3:3">
       <c r="C184">
         <v>1395.2012</v>
       </c>
     </row>
-    <row r="185" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:3">
       <c r="C185">
         <v>1407.7113999999999</v>
       </c>
     </row>
-    <row r="186" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="3:3">
       <c r="C186">
         <v>1407.7227</v>
       </c>
     </row>
-    <row r="187" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="3:3">
       <c r="C187">
         <v>1408.7011</v>
       </c>
     </row>
-    <row r="188" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="3:3">
       <c r="C188" s="6">
         <v>1423.7064</v>
       </c>
     </row>
-    <row r="189" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="3:3">
       <c r="C189" s="6">
         <v>1437.722</v>
       </c>
     </row>
-    <row r="190" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="3:3">
       <c r="C190">
         <v>1440.7217000000001</v>
       </c>
     </row>
-    <row r="191" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="3:3">
       <c r="C191">
         <v>1451.2275</v>
       </c>
     </row>
-    <row r="192" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="3:3">
       <c r="C192">
         <v>1452.7273</v>
       </c>
     </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:3">
       <c r="C193">
         <v>1458.7329</v>
       </c>
     </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="3:3">
       <c r="C194">
         <v>1464.7329</v>
       </c>
     </row>
-    <row r="195" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:3">
       <c r="C195">
         <v>1465.7407000000001</v>
       </c>
     </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:3">
       <c r="C196">
         <v>1467.2406000000001</v>
       </c>
     </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:3">
       <c r="C197">
         <v>1472.7485999999999</v>
       </c>
     </row>
-    <row r="198" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:3">
       <c r="C198">
         <v>1473.7382</v>
       </c>
     </row>
-    <row r="199" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:3">
       <c r="C199">
         <v>1480.7460000000001</v>
       </c>
     </row>
-    <row r="200" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:3">
       <c r="C200">
         <v>1481.2562</v>
       </c>
     </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="3:3">
       <c r="C201">
         <v>1481.7482</v>
       </c>
     </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="3:3">
       <c r="C202">
         <v>1482.2457999999999</v>
       </c>
     </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="3:3">
       <c r="C203">
         <v>1489.2537</v>
       </c>
     </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="3:3">
       <c r="C204">
         <v>1497.2511</v>
       </c>
     </row>
-    <row r="205" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="3:3">
       <c r="C205">
         <v>1502.7535</v>
       </c>
     </row>
-    <row r="206" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="3:3">
       <c r="C206">
         <v>1510.7747999999999</v>
       </c>
     </row>
-    <row r="207" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:3">
       <c r="C207">
         <v>1511.7588000000001</v>
       </c>
     </row>
-    <row r="208" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:3">
       <c r="C208">
         <v>1516.259</v>
       </c>
     </row>
-    <row r="209" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="3:3">
       <c r="C209">
         <v>1517.7588000000001</v>
       </c>
     </row>
-    <row r="210" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="3:3">
       <c r="C210">
         <v>1531.2642000000001</v>
       </c>
     </row>
-    <row r="211" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="3:3">
       <c r="C211">
         <v>1532.7641000000001</v>
       </c>
     </row>
-    <row r="212" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="3:3">
       <c r="C212">
         <v>1540.7853</v>
       </c>
     </row>
-    <row r="213" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="3:3">
       <c r="C213">
         <v>1545.7774999999999</v>
       </c>
     </row>
-    <row r="214" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="3:3">
       <c r="C214">
         <v>1546.2695000000001</v>
       </c>
     </row>
-    <row r="215" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="3:3">
       <c r="C215">
         <v>1552.7853</v>
       </c>
     </row>
-    <row r="216" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="3:3">
       <c r="C216">
         <v>1554.8009999999999</v>
       </c>
     </row>
-    <row r="217" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="3:3">
       <c r="C217">
         <v>1560.7828</v>
       </c>
     </row>
-    <row r="218" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="3:3">
       <c r="C218">
         <v>1561.2747999999999</v>
       </c>
     </row>
-    <row r="219" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="3:3">
       <c r="C219">
         <v>1567.7906</v>
       </c>
     </row>
-    <row r="220" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="3:3">
       <c r="C220">
         <v>1570.7959000000001</v>
       </c>
     </row>
-    <row r="221" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="3:3">
       <c r="C221">
         <v>1574.7893999999999</v>
       </c>
     </row>
-    <row r="222" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="3:3">
       <c r="C222">
         <v>1575.7881</v>
       </c>
     </row>
-    <row r="223" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="3:3">
       <c r="C223">
         <v>1576.2982999999999</v>
       </c>
     </row>
-    <row r="224" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="3:3">
       <c r="C224">
         <v>1582.7959000000001</v>
       </c>
     </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="3:3">
       <c r="C225">
         <v>1590.7934</v>
       </c>
     </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:3">
       <c r="C226">
         <v>1591.3036</v>
       </c>
     </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:3">
       <c r="C227">
         <v>1595.8275000000001</v>
       </c>
     </row>
-    <row r="228" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:3">
       <c r="C228">
         <v>1597.7955999999999</v>
       </c>
     </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:3">
       <c r="C229">
         <v>1605.7986000000001</v>
       </c>
     </row>
-    <row r="230" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:3">
       <c r="C230">
         <v>1607.8275000000001</v>
       </c>
     </row>
-    <row r="231" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:3">
       <c r="C231">
         <v>1611.8225</v>
       </c>
     </row>
-    <row r="232" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:3">
       <c r="C232">
         <v>1625.3167000000001</v>
       </c>
     </row>
-    <row r="233" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:3">
       <c r="C233">
         <v>1627.8061</v>
       </c>
     </row>
-    <row r="234" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:3">
       <c r="C234">
         <v>1640.3219999999999</v>
       </c>
     </row>
-    <row r="235" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:3">
       <c r="C235">
         <v>1654.8352</v>
       </c>
     </row>
-    <row r="236" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="3:3">
       <c r="C236">
         <v>1655.3271999999999</v>
       </c>
     </row>
-    <row r="237" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="3:3">
       <c r="C237">
         <v>1668.8326999999999</v>
       </c>
     </row>
-    <row r="238" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="3:3">
       <c r="C238">
         <v>1669.8405</v>
       </c>
     </row>
-    <row r="239" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="3:3">
       <c r="C239">
         <v>1676.8483000000001</v>
       </c>
     </row>
-    <row r="240" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="3:3">
       <c r="C240">
         <v>1684.8458000000001</v>
       </c>
     </row>
-    <row r="241" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="3:3">
       <c r="C241">
         <v>1685.848</v>
       </c>
     </row>
-    <row r="242" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="3:3">
       <c r="C242">
         <v>1699.8511000000001</v>
       </c>
     </row>
-    <row r="243" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="3:3">
       <c r="C243">
         <v>1699.8635999999999</v>
       </c>
     </row>
-    <row r="244" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="3:3">
       <c r="C244">
         <v>1714.8744999999999</v>
       </c>
     </row>
-    <row r="245" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="3:3">
       <c r="C245">
         <v>1715.8586</v>
       </c>
     </row>
-    <row r="246" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="3:3">
       <c r="C246">
         <v>1726.8744999999999</v>
       </c>
     </row>
-    <row r="247" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="3:3">
       <c r="C247">
         <v>1727.8697999999999</v>
       </c>
     </row>
-    <row r="248" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="3:3">
       <c r="C248">
         <v>1728.8902</v>
       </c>
     </row>
-    <row r="249" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="3:3">
       <c r="C249">
         <v>1741.8853999999999</v>
       </c>
     </row>
-    <row r="250" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="3:3">
       <c r="C250">
         <v>1744.8851</v>
       </c>
     </row>
-    <row r="251" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="3:3">
       <c r="C251">
         <v>1756.8851</v>
       </c>
     </row>
-    <row r="252" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="3:3">
       <c r="C252">
         <v>1758.9007999999999</v>
       </c>
     </row>
-    <row r="253" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="3:3">
       <c r="C253">
         <v>1763.8929000000001</v>
       </c>
     </row>
-    <row r="254" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="3:3">
       <c r="C254">
         <v>1774.8957</v>
       </c>
     </row>
-    <row r="255" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="3:3">
       <c r="C255">
         <v>1778.8982000000001</v>
       </c>
     </row>
-    <row r="256" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="3:3">
       <c r="C256">
         <v>1785.9117000000001</v>
       </c>
     </row>
-    <row r="257" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="3:3">
       <c r="C257">
         <v>1793.9034999999999</v>
       </c>
     </row>
-    <row r="258" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="3:3">
       <c r="C258">
         <v>1799.9273000000001</v>
       </c>
     </row>
-    <row r="259" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="3:3">
       <c r="C259">
         <v>1801.8952999999999</v>
       </c>
     </row>
-    <row r="260" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="3:3">
       <c r="C260">
         <v>1815.9222</v>
       </c>
     </row>
-    <row r="261" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="3:3">
       <c r="C261">
         <v>1831.9059</v>
       </c>
     </row>
-    <row r="262" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="3:3">
       <c r="C262">
         <v>1842.9219000000001</v>
       </c>
     </row>
-    <row r="263" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="3:3">
       <c r="C263">
         <v>1870.9644000000001</v>
       </c>
     </row>
-    <row r="264" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="3:3">
       <c r="C264">
         <v>1872.9324999999999</v>
       </c>
     </row>
-    <row r="265" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="3:3">
       <c r="C265">
         <v>1886.9481000000001</v>
       </c>
     </row>
-    <row r="266" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="3:3">
       <c r="C266">
         <v>1889.9477999999999</v>
       </c>
     </row>
-    <row r="267" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="3:3">
       <c r="C267">
         <v>1901.9590000000001</v>
       </c>
     </row>
-    <row r="268" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="3:3">
       <c r="C268">
         <v>1913.9590000000001</v>
       </c>
     </row>
-    <row r="269" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="3:3">
       <c r="C269">
         <v>1915.9747</v>
       </c>
     </row>
-    <row r="270" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="3:3">
       <c r="C270">
         <v>1918.9743000000001</v>
       </c>
     </row>
-    <row r="271" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="3:3">
       <c r="C271">
         <v>1930.9743000000001</v>
       </c>
     </row>
-    <row r="272" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="3:3">
       <c r="C272">
         <v>1931.9695999999999</v>
       </c>
     </row>
-    <row r="273" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="3:3">
       <c r="C273">
         <v>1932.99</v>
       </c>
     </row>
-    <row r="274" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="3:3">
       <c r="C274">
         <v>1944.99</v>
       </c>
     </row>
-    <row r="275" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="3:3">
       <c r="C275">
         <v>1945.9852000000001</v>
       </c>
     </row>
-    <row r="276" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="3:3">
       <c r="C276">
         <v>1948.9848999999999</v>
       </c>
     </row>
-    <row r="277" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="3:3">
       <c r="C277">
         <v>1960.0009</v>
       </c>
     </row>
-    <row r="278" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="3:3">
       <c r="C278">
         <v>1960.9848999999999</v>
       </c>
     </row>
-    <row r="279" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="3:3">
       <c r="C279">
         <v>1961.9801</v>
       </c>
     </row>
-    <row r="280" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="3:3">
       <c r="C280">
         <v>1963.0005000000001</v>
       </c>
     </row>
-    <row r="281" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="3:3">
       <c r="C281">
         <v>1990.0114000000001</v>
       </c>
@@ -13102,13 +13102,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5905CE10-0E48-42B8-B31E-41CE897F3A64}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="47.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>212</v>
       </c>
@@ -13116,7 +13116,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>214</v>
       </c>
@@ -13124,7 +13124,7 @@
         <v>45557</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>215</v>
       </c>
@@ -13132,7 +13132,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>216</v>
       </c>
@@ -13140,22 +13140,22 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="66" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="66">
       <c r="B11" s="4" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="B14" t="s">
         <v>230</v>
       </c>
@@ -13167,6 +13167,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="f82b70a8-9591-478e-a6d5-bf315b83c485" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100B01D25D17823C344A9D69518AF56DC62" ma:contentTypeVersion="6" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f29605d1c82d3d43c74cd3efc573dd15">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f82b70a8-9591-478e-a6d5-bf315b83c485" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d7d0483a01e3419b531383906934819f" ns3:_="">
     <xsd:import namespace="f82b70a8-9591-478e-a6d5-bf315b83c485"/>
@@ -13322,24 +13339,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFEF422C-B8D3-4F6C-950A-A4DFD4067B7B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="f82b70a8-9591-478e-a6d5-bf315b83c485"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="f82b70a8-9591-478e-a6d5-bf315b83c485" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80E8E46-C8F1-4EA0-9D75-58D6A3F6209E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3840DE93-E5DB-49F7-A595-E7AEB960EE63}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13355,28 +13379,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80E8E46-C8F1-4EA0-9D75-58D6A3F6209E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFEF422C-B8D3-4F6C-950A-A4DFD4067B7B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="f82b70a8-9591-478e-a6d5-bf315b83c485"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>